--- a/artfynd/A 63804-2023 artfynd.xlsx
+++ b/artfynd/A 63804-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63804-2023 artfynd.xlsx
+++ b/artfynd/A 63804-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,39 +675,30 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104854511</v>
+        <v>104854506</v>
       </c>
       <c r="B2" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>4398</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vitvaxing agg.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>366512.8809685697</v>
+        <v>366506</v>
       </c>
       <c r="R2" t="n">
-        <v>6548977.777554598</v>
+        <v>6548961</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -748,19 +739,9 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -795,12 +776,7 @@
         <v>110259882</v>
       </c>
       <c r="B3" t="n">
-        <v>104838</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -848,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>366546.0032288969</v>
+        <v>366546</v>
       </c>
       <c r="R3" t="n">
-        <v>6548981.255411033</v>
+        <v>6548981</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -881,19 +857,9 @@
           <t>2023-06-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -923,6 +889,206 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104854511</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjuke, Åmål, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>366513</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6548978</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104854534</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjuke, Åmål, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>366546</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6549095</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åmål</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-09-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering SUNDH MILJÖ AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
